--- a/data/vannmiljo_duplicates_stations.xlsx
+++ b/data/vannmiljo_duplicates_stations.xlsx
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>29</v>
+        <v>260</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>260</v>
+        <v>29</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.1</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>9.1</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>4.1</v>
+        <v>31</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>31</v>
+        <v>4.1</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>0</v>
       </c>
       <c r="AB358" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="AC358" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>0</v>
       </c>
       <c r="AB359" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="AC359" t="inlineStr">
         <is>
@@ -49382,7 +49382,7 @@
         <v>0</v>
       </c>
       <c r="AB368" t="n">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="AC368" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>0</v>
       </c>
       <c r="AB369" t="n">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AC369" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>0</v>
       </c>
       <c r="AB372" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="AC372" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>0</v>
       </c>
       <c r="AB373" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="AC373" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>1</v>
       </c>
       <c r="AB378" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AC378" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>1</v>
       </c>
       <c r="AB379" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AC379" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>1</v>
       </c>
       <c r="AB380" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AC380" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>1</v>
       </c>
       <c r="AB381" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AC381" t="inlineStr">
         <is>
@@ -51244,7 +51244,7 @@
         <v>1</v>
       </c>
       <c r="AB382" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AC382" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
         <v>1</v>
       </c>
       <c r="AB383" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AC383" t="inlineStr">
         <is>
@@ -51510,7 +51510,7 @@
         <v>1</v>
       </c>
       <c r="AB384" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AC384" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>1</v>
       </c>
       <c r="AB385" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AC385" t="inlineStr">
         <is>
@@ -52042,7 +52042,7 @@
         <v>1</v>
       </c>
       <c r="AB388" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AC388" t="inlineStr">
         <is>
@@ -52175,7 +52175,7 @@
         <v>1</v>
       </c>
       <c r="AB389" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AC389" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>1</v>
       </c>
       <c r="AB390" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AC390" t="inlineStr">
         <is>
@@ -52441,7 +52441,7 @@
         <v>1</v>
       </c>
       <c r="AB391" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AC391" t="inlineStr">
         <is>
@@ -53372,7 +53372,7 @@
         <v>1</v>
       </c>
       <c r="AB398" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="AC398" t="inlineStr">
         <is>
@@ -53505,7 +53505,7 @@
         <v>1</v>
       </c>
       <c r="AB399" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AC399" t="inlineStr">
         <is>
@@ -53638,7 +53638,7 @@
         <v>1</v>
       </c>
       <c r="AB400" t="n">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="AC400" t="inlineStr">
         <is>
@@ -53771,7 +53771,7 @@
         <v>1</v>
       </c>
       <c r="AB401" t="n">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="AC401" t="inlineStr">
         <is>
@@ -54702,7 +54702,7 @@
         <v>0</v>
       </c>
       <c r="AB408" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="AC408" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>0</v>
       </c>
       <c r="AB409" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="AC409" t="inlineStr">
         <is>
@@ -56032,7 +56032,7 @@
         <v>0</v>
       </c>
       <c r="AB418" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="AC418" t="inlineStr">
         <is>
@@ -56165,7 +56165,7 @@
         <v>0</v>
       </c>
       <c r="AB419" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="AC419" t="inlineStr">
         <is>
@@ -57362,7 +57362,7 @@
         <v>0</v>
       </c>
       <c r="AB428" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AC428" t="inlineStr">
         <is>
@@ -57495,7 +57495,7 @@
         <v>0</v>
       </c>
       <c r="AB429" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AC429" t="inlineStr">
         <is>
@@ -60022,7 +60022,7 @@
         <v>0</v>
       </c>
       <c r="AB448" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC448" t="inlineStr">
         <is>
@@ -60155,7 +60155,7 @@
         <v>0</v>
       </c>
       <c r="AB449" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC449" t="inlineStr">
         <is>
@@ -61352,7 +61352,7 @@
         <v>0</v>
       </c>
       <c r="AB458" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC458" t="inlineStr">
         <is>
@@ -61485,7 +61485,7 @@
         <v>0</v>
       </c>
       <c r="AB459" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC459" t="inlineStr">
         <is>
@@ -62682,7 +62682,7 @@
         <v>0</v>
       </c>
       <c r="AB468" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="AC468" t="inlineStr">
         <is>
@@ -62815,7 +62815,7 @@
         <v>0</v>
       </c>
       <c r="AB469" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="AC469" t="inlineStr">
         <is>
@@ -64012,7 +64012,7 @@
         <v>0</v>
       </c>
       <c r="AB478" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="AC478" t="inlineStr">
         <is>
@@ -64145,7 +64145,7 @@
         <v>0</v>
       </c>
       <c r="AB479" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="AC479" t="inlineStr">
         <is>
@@ -65342,7 +65342,7 @@
         <v>0</v>
       </c>
       <c r="AB488" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AC488" t="inlineStr">
         <is>
@@ -65475,7 +65475,7 @@
         <v>0</v>
       </c>
       <c r="AB489" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AC489" t="inlineStr">
         <is>
@@ -66672,7 +66672,7 @@
         <v>0</v>
       </c>
       <c r="AB498" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AC498" t="inlineStr">
         <is>
@@ -66805,7 +66805,7 @@
         <v>0</v>
       </c>
       <c r="AB499" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AC499" t="inlineStr">
         <is>
@@ -78376,7 +78376,7 @@
         <v>0</v>
       </c>
       <c r="AB586" t="n">
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="AC586" t="inlineStr">
         <is>
@@ -78509,7 +78509,7 @@
         <v>0</v>
       </c>
       <c r="AB587" t="n">
-        <v>470</v>
+        <v>510</v>
       </c>
       <c r="AC587" t="inlineStr">
         <is>
